--- a/DateBase/orders/Nha Thu_2026-5-13.xlsx
+++ b/DateBase/orders/Nha Thu_2026-5-13.xlsx
@@ -691,6 +691,9 @@
       <c r="C31" t="str">
         <v>321_雪柳叶_Spiraea  leaves_undefined_1bunch</v>
       </c>
+      <c r="F31" t="str">
+        <v>15</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -749,7 +752,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0105541010101515105510510151010105510101510151010150</v>
+        <v>01055410101015151055105101510101055101015101510101515</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-5-13.xlsx
+++ b/DateBase/orders/Nha Thu_2026-5-13.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L50"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -695,9 +695,173 @@
         <v>15</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>1</v>
+      </c>
+      <c r="C32" t="str">
+        <v>325_小盼草_Northern Sea Oats_undefined_1bunch</v>
+      </c>
+      <c r="F32" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="str">
+        <v>503_丁香花 粉_lilac pink_undefined_1bunch</v>
+      </c>
+      <c r="F33" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="str">
+        <v>738_鸢尾花蓝_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F34" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="str">
+        <v>533_风车果_scabiosa pods_undefined_1bunch</v>
+      </c>
+      <c r="F35" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="str">
+        <v>880_铁线莲浅紫_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F36" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="str">
+        <v>770_弯葱_undefined_undefined_10stems</v>
+      </c>
+      <c r="F37" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" xml:space="preserve">
+      <c r="C38" t="str" xml:space="preserve">
+        <v xml:space="preserve">542_吊米 红_hanging amaranthus
+red_undefined_1bunch</v>
+      </c>
+      <c r="F38" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="str">
+        <v>322_喷泉草_Grasses Panicum_undefined_1bunch</v>
+      </c>
+      <c r="F39" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>2</v>
+      </c>
+      <c r="C40" t="str">
+        <v>521_商陆_phytolacca acinosa _undefined_1bunch</v>
+      </c>
+      <c r="F40" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41" xml:space="preserve">
+      <c r="C41" t="str" xml:space="preserve">
+        <v xml:space="preserve">740_袋鼠爪橙_Kangaroo Paw
+red /green /orange / yellow_undefined_1bunch</v>
+      </c>
+      <c r="F41" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" t="str">
+        <v>329_柔丝_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F42" t="str">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="str">
+        <v>558_油画小菊_Helenium_undefined_1bunch</v>
+      </c>
+      <c r="F43" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="str">
+        <v>11_香槟洋桔梗_Champagne Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F44" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="str">
+        <v>612_康乃馨古巴爱情_cuba love_undefined_20stems</v>
+      </c>
+      <c r="F45" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" t="str">
+        <v>48_香格里拉_undefined_Gerbera L._10stems</v>
+      </c>
+      <c r="F46" t="str">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" t="str">
+        <v>46_拉丝橙_Spider orange_Gerbera L._20stems</v>
+      </c>
+      <c r="F47" t="str">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="48" xml:space="preserve">
+      <c r="A48" t="str">
+        <v>3</v>
+      </c>
+      <c r="C48" t="str" xml:space="preserve">
+        <v xml:space="preserve">448_吊米 绿_hanging amaranthus
+green_undefined_1bunch</v>
+      </c>
+      <c r="F48" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="C49" t="str">
+        <v>384_奶油向日葵_sunflower cream_undefined_1bunch</v>
+      </c>
+      <c r="F49" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="C50" t="str">
+        <v>46_拉丝橙_Spider orange_Gerbera L._20stems</v>
+      </c>
+      <c r="F50" t="str">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L50"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -752,7 +916,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01055410101015151055105101510101055101015101510101515</v>
+        <v>0105541010101515105510510151010105510101510151010151551551535551565020125169566</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-5-13.xlsx
+++ b/DateBase/orders/Nha Thu_2026-5-13.xlsx
@@ -918,6 +918,9 @@
       <c r="G2" t="str">
         <v>0105541010101515105510510151010105510101510151010151551551535551565020125169566</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
